--- a/public/course_upload_template.xlsx
+++ b/public/course_upload_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,30 +421,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CSC1001</v>
+        <v>EL0101</v>
       </c>
       <c r="B2" t="str">
-        <v>Biology</v>
+        <v>Power Enginer</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="str">
-        <v>LEVEL_200</v>
+        <v>LEVEL_100</v>
       </c>
       <c r="E2" t="str">
         <v>FIRST_SEMESTER</v>
       </c>
       <c r="F2" t="str">
-        <v>BSc</v>
+        <v>ELP</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EL0101</v>
+        <v>OEE</v>
       </c>
       <c r="B3" t="str">
-        <v>Power Enginer</v>
+        <v>physics</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -456,32 +456,12 @@
         <v>FIRST_SEMESTER</v>
       </c>
       <c r="F3" t="str">
-        <v>ELP</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>OEE</v>
-      </c>
-      <c r="B4" t="str">
-        <v>physics</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="str">
-        <v>LEVEL_100</v>
-      </c>
-      <c r="E4" t="str">
-        <v>FIRST_SEMESTER</v>
-      </c>
-      <c r="F4" t="str">
         <v>ELP</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>